--- a/dcf/MRVL.xlsx
+++ b/dcf/MRVL.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.1321710012345207</v>
+        <v>0.1320459789085889</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.1371710012345208</v>
+        <v>0.1370459789085889</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.1421710012345208</v>
+        <v>0.1420459789085889</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1471710012345208</v>
+        <v>0.1470459789085889</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1521710012345208</v>
+        <v>0.1520459789085889</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1571710012345208</v>
+        <v>0.1570459789085889</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1621710012345208</v>
+        <v>0.1620459789085889</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>93.52378053132946</v>
+        <v>77.88828058533871</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>90.23870819899575</v>
+        <v>75.22155025389239</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>87.09557200150293</v>
+        <v>72.66892975201409</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>84.08743087931204</v>
+        <v>70.22486240579696</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>81.20771661132673</v>
+        <v>67.88408937507259</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>78.45021213384292</v>
+        <v>65.64163235480211</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>75.80903121215968</v>
+        <v>63.49277735494521</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>99.50744832120876</v>
+        <v>82.64491540863764</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>95.96442653341229</v>
+        <v>79.77310958573614</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>92.57552012274738</v>
+        <v>77.02509739709879</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>89.33316339168658</v>
+        <v>74.39482546151008</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>86.23019803850354</v>
+        <v>71.87656571416161</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>83.25984942606526</v>
+        <v>69.4648964774276</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>80.41570433304958</v>
+        <v>67.15468471333863</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>105.4911161110881</v>
+        <v>87.40155023193661</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>101.6901448678288</v>
+        <v>84.3246689175799</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>98.05546824399184</v>
+        <v>81.38126504218351</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>94.57889590406113</v>
+        <v>78.56478851722322</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>91.25267946568034</v>
+        <v>75.86904205325064</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>88.06948671828761</v>
+        <v>73.28816060005309</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>85.02237745393948</v>
+        <v>70.81659207173206</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>111.4747839009674</v>
+        <v>92.15818505523553</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>107.4158632022453</v>
+        <v>88.87622824942366</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>103.5354163652363</v>
+        <v>85.73743268726822</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>99.82462841643566</v>
+        <v>82.73475157293635</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>96.27516089285716</v>
+        <v>79.86151839233965</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>92.87912401050993</v>
+        <v>77.11142472267861</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>89.62905057482936</v>
+        <v>74.47849943012548</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>117.4584516908466</v>
+        <v>96.9148198785345</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>113.1415815366619</v>
+        <v>93.42778758126741</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>109.0153644864807</v>
+        <v>90.09360033235295</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>105.0703609288102</v>
+        <v>86.90471462864947</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>101.297642320034</v>
+        <v>83.85399473142868</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>97.68876130273226</v>
+        <v>80.93468884530409</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>94.23572369571927</v>
+        <v>78.14040678851892</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>123.4421194807259</v>
+        <v>101.6714547018334</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>118.8672998710784</v>
+        <v>97.97934691311114</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>114.4953126077252</v>
+        <v>94.44976797743767</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>110.3160934411847</v>
+        <v>91.07467768436261</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>106.3201237472108</v>
+        <v>87.84647107051771</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>102.4983985949546</v>
+        <v>84.75795296792958</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>98.84239681660915</v>
+        <v>81.80231414691232</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>129.4257872706052</v>
+        <v>106.4280895251324</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>124.5930182054949</v>
+        <v>102.5309062449549</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>119.9752607289696</v>
+        <v>98.80593562252238</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>115.5618259535593</v>
+        <v>95.24464074007574</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>111.3426051743876</v>
+        <v>91.83894740960673</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>107.3080358871769</v>
+        <v>88.58121709055507</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>103.449069937499</v>
+        <v>85.46422150530576</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>245.2899932861328</v>
+        <v>231.4700012207031</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1471710012345208</v>
+        <v>0.1470459789085889</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.064100943485939</v>
+        <v>1.080236269866151</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>245.2899932861328</v>
+        <v>231.4700012207031</v>
       </c>
     </row>
     <row r="49">
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>99.82462841643566</v>
+        <v>82.73475157293635</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>132.8787856559209</v>
+        <v>107.3795575152652</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>74.30246667291391</v>
+        <v>63.19922383212479</v>
       </c>
     </row>
     <row r="59">
